--- a/Supportsystem.xlsx
+++ b/Supportsystem.xlsx
@@ -342,7 +342,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Saker per kategori</a:t>
+              <a:t>Topp 10 saker pr kategori</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -366,12 +366,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$35:$A$42</f>
+              <f>'Dashboard'!$A$35:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$35:$B$42</f>
+              <f>'Dashboard'!$B$35:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -426,7 +426,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Saker per ansvarlig</a:t>
+              <a:t>Topp 10 saker pr ansvarlig</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -450,12 +450,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$C$27:$C$32</f>
+              <f>'Dashboard'!$C$27:$C$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$27:$D$32</f>
+              <f>'Dashboard'!$D$27:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -1464,7 +1464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1479,8 +1479,18 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col hidden="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col hidden="1" min="16" max="16"/>
+    <col hidden="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col hidden="1" min="21" max="21"/>
+    <col hidden="1" min="22" max="22"/>
+    <col hidden="1" min="23" max="23"/>
+    <col hidden="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1496,6 +1506,104 @@
           <t>Alle tall og diagrammer oppdateres automatisk ut fra arkfanen Saker.</t>
         </is>
       </c>
+      <c r="M2">
+        <f>IFERROR(INDEX(Kategorier,1),"")</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>IF($M2="",0,COUNTIFS(Saker!$F$2:$F$501,$M2))</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>IF($N2=0,-999999,$N2-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>IFERROR(INDEX(Ansatte,1),"")</f>
+        <v/>
+      </c>
+      <c r="Q2">
+        <f>IF($P2="",0,COUNTIFS(Saker!$L$2:$L$501,$P2))</f>
+        <v/>
+      </c>
+      <c r="R2">
+        <f>IF($Q2=0,-999999,$Q2-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S2">
+        <f>MATCH(LARGE($O$2:$O$51,1),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T2">
+        <f>INDEX($N$2:$N$51,$S2)</f>
+        <v/>
+      </c>
+      <c r="U2">
+        <f>INDEX($M$2:$M$51,$S2)</f>
+        <v/>
+      </c>
+      <c r="V2">
+        <f>MATCH(LARGE($R$2:$R$51,1),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W2">
+        <f>INDEX($Q$2:$Q$51,$V2)</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>INDEX($P$2:$P$51,$V2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="M3">
+        <f>IFERROR(INDEX(Kategorier,2),"")</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>IF($M3="",0,COUNTIFS(Saker!$F$2:$F$501,$M3))</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>IF($N3=0,-999999,$N3-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>IFERROR(INDEX(Ansatte,2),"")</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>IF($P3="",0,COUNTIFS(Saker!$L$2:$L$501,$P3))</f>
+        <v/>
+      </c>
+      <c r="R3">
+        <f>IF($Q3=0,-999999,$Q3-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S3">
+        <f>MATCH(LARGE($O$2:$O$51,2),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T3">
+        <f>INDEX($N$2:$N$51,$S3)</f>
+        <v/>
+      </c>
+      <c r="U3">
+        <f>INDEX($M$2:$M$51,$S3)</f>
+        <v/>
+      </c>
+      <c r="V3">
+        <f>MATCH(LARGE($R$2:$R$51,2),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W3">
+        <f>INDEX($Q$2:$Q$51,$V3)</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>INDEX($P$2:$P$51,$V3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1534,6 +1642,54 @@
         </is>
       </c>
       <c r="L4" s="4" t="n"/>
+      <c r="M4">
+        <f>IFERROR(INDEX(Kategorier,3),"")</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>IF($M4="",0,COUNTIFS(Saker!$F$2:$F$501,$M4))</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>IF($N4=0,-999999,$N4-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>IFERROR(INDEX(Ansatte,3),"")</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>IF($P4="",0,COUNTIFS(Saker!$L$2:$L$501,$P4))</f>
+        <v/>
+      </c>
+      <c r="R4">
+        <f>IF($Q4=0,-999999,$Q4-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S4">
+        <f>MATCH(LARGE($O$2:$O$51,3),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T4">
+        <f>INDEX($N$2:$N$51,$S4)</f>
+        <v/>
+      </c>
+      <c r="U4">
+        <f>INDEX($M$2:$M$51,$S4)</f>
+        <v/>
+      </c>
+      <c r="V4">
+        <f>MATCH(LARGE($R$2:$R$51,3),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W4">
+        <f>INDEX($Q$2:$Q$51,$V4)</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>INDEX($P$2:$P$51,$V4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5">
@@ -1560,19 +1716,752 @@
         <f>COUNTA(Kunnskapsbase!$B$2:$B$301)</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="3" customHeight="1"/>
-    <row r="25" ht="12" customHeight="1"/>
+      <c r="M5">
+        <f>IFERROR(INDEX(Kategorier,4),"")</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>IF($M5="",0,COUNTIFS(Saker!$F$2:$F$501,$M5))</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>IF($N5=0,-999999,$N5-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>IFERROR(INDEX(Ansatte,4),"")</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>IF($P5="",0,COUNTIFS(Saker!$L$2:$L$501,$P5))</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>IF($Q5=0,-999999,$Q5-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S5">
+        <f>MATCH(LARGE($O$2:$O$51,4),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>INDEX($N$2:$N$51,$S5)</f>
+        <v/>
+      </c>
+      <c r="U5">
+        <f>INDEX($M$2:$M$51,$S5)</f>
+        <v/>
+      </c>
+      <c r="V5">
+        <f>MATCH(LARGE($R$2:$R$51,4),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W5">
+        <f>INDEX($Q$2:$Q$51,$V5)</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>INDEX($P$2:$P$51,$V5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="M6">
+        <f>IFERROR(INDEX(Kategorier,5),"")</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>IF($M6="",0,COUNTIFS(Saker!$F$2:$F$501,$M6))</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>IF($N6=0,-999999,$N6-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>IFERROR(INDEX(Ansatte,5),"")</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>IF($P6="",0,COUNTIFS(Saker!$L$2:$L$501,$P6))</f>
+        <v/>
+      </c>
+      <c r="R6">
+        <f>IF($Q6=0,-999999,$Q6-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S6">
+        <f>MATCH(LARGE($O$2:$O$51,5),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>INDEX($N$2:$N$51,$S6)</f>
+        <v/>
+      </c>
+      <c r="U6">
+        <f>INDEX($M$2:$M$51,$S6)</f>
+        <v/>
+      </c>
+      <c r="V6">
+        <f>MATCH(LARGE($R$2:$R$51,5),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W6">
+        <f>INDEX($Q$2:$Q$51,$V6)</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>INDEX($P$2:$P$51,$V6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="3" customHeight="1">
+      <c r="M7">
+        <f>IFERROR(INDEX(Kategorier,6),"")</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>IF($M7="",0,COUNTIFS(Saker!$F$2:$F$501,$M7))</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>IF($N7=0,-999999,$N7-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>IFERROR(INDEX(Ansatte,6),"")</f>
+        <v/>
+      </c>
+      <c r="Q7">
+        <f>IF($P7="",0,COUNTIFS(Saker!$L$2:$L$501,$P7))</f>
+        <v/>
+      </c>
+      <c r="R7">
+        <f>IF($Q7=0,-999999,$Q7-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S7">
+        <f>MATCH(LARGE($O$2:$O$51,6),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T7">
+        <f>INDEX($N$2:$N$51,$S7)</f>
+        <v/>
+      </c>
+      <c r="U7">
+        <f>INDEX($M$2:$M$51,$S7)</f>
+        <v/>
+      </c>
+      <c r="V7">
+        <f>MATCH(LARGE($R$2:$R$51,6),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W7">
+        <f>INDEX($Q$2:$Q$51,$V7)</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>INDEX($P$2:$P$51,$V7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="M8">
+        <f>IFERROR(INDEX(Kategorier,7),"")</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>IF($M8="",0,COUNTIFS(Saker!$F$2:$F$501,$M8))</f>
+        <v/>
+      </c>
+      <c r="O8">
+        <f>IF($N8=0,-999999,$N8-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P8">
+        <f>IFERROR(INDEX(Ansatte,7),"")</f>
+        <v/>
+      </c>
+      <c r="Q8">
+        <f>IF($P8="",0,COUNTIFS(Saker!$L$2:$L$501,$P8))</f>
+        <v/>
+      </c>
+      <c r="R8">
+        <f>IF($Q8=0,-999999,$Q8-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S8">
+        <f>MATCH(LARGE($O$2:$O$51,7),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T8">
+        <f>INDEX($N$2:$N$51,$S8)</f>
+        <v/>
+      </c>
+      <c r="U8">
+        <f>INDEX($M$2:$M$51,$S8)</f>
+        <v/>
+      </c>
+      <c r="V8">
+        <f>MATCH(LARGE($R$2:$R$51,7),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W8">
+        <f>INDEX($Q$2:$Q$51,$V8)</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>INDEX($P$2:$P$51,$V8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="M9">
+        <f>IFERROR(INDEX(Kategorier,8),"")</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>IF($M9="",0,COUNTIFS(Saker!$F$2:$F$501,$M9))</f>
+        <v/>
+      </c>
+      <c r="O9">
+        <f>IF($N9=0,-999999,$N9-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P9">
+        <f>IFERROR(INDEX(Ansatte,8),"")</f>
+        <v/>
+      </c>
+      <c r="Q9">
+        <f>IF($P9="",0,COUNTIFS(Saker!$L$2:$L$501,$P9))</f>
+        <v/>
+      </c>
+      <c r="R9">
+        <f>IF($Q9=0,-999999,$Q9-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S9">
+        <f>MATCH(LARGE($O$2:$O$51,8),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T9">
+        <f>INDEX($N$2:$N$51,$S9)</f>
+        <v/>
+      </c>
+      <c r="U9">
+        <f>INDEX($M$2:$M$51,$S9)</f>
+        <v/>
+      </c>
+      <c r="V9">
+        <f>MATCH(LARGE($R$2:$R$51,8),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>INDEX($Q$2:$Q$51,$V9)</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>INDEX($P$2:$P$51,$V9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="M10">
+        <f>IFERROR(INDEX(Kategorier,9),"")</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>IF($M10="",0,COUNTIFS(Saker!$F$2:$F$501,$M10))</f>
+        <v/>
+      </c>
+      <c r="O10">
+        <f>IF($N10=0,-999999,$N10-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P10">
+        <f>IFERROR(INDEX(Ansatte,9),"")</f>
+        <v/>
+      </c>
+      <c r="Q10">
+        <f>IF($P10="",0,COUNTIFS(Saker!$L$2:$L$501,$P10))</f>
+        <v/>
+      </c>
+      <c r="R10">
+        <f>IF($Q10=0,-999999,$Q10-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S10">
+        <f>MATCH(LARGE($O$2:$O$51,9),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T10">
+        <f>INDEX($N$2:$N$51,$S10)</f>
+        <v/>
+      </c>
+      <c r="U10">
+        <f>INDEX($M$2:$M$51,$S10)</f>
+        <v/>
+      </c>
+      <c r="V10">
+        <f>MATCH(LARGE($R$2:$R$51,9),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W10">
+        <f>INDEX($Q$2:$Q$51,$V10)</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>INDEX($P$2:$P$51,$V10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="M11">
+        <f>IFERROR(INDEX(Kategorier,10),"")</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>IF($M11="",0,COUNTIFS(Saker!$F$2:$F$501,$M11))</f>
+        <v/>
+      </c>
+      <c r="O11">
+        <f>IF($N11=0,-999999,$N11-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P11">
+        <f>IFERROR(INDEX(Ansatte,10),"")</f>
+        <v/>
+      </c>
+      <c r="Q11">
+        <f>IF($P11="",0,COUNTIFS(Saker!$L$2:$L$501,$P11))</f>
+        <v/>
+      </c>
+      <c r="R11">
+        <f>IF($Q11=0,-999999,$Q11-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="S11">
+        <f>MATCH(LARGE($O$2:$O$51,10),$O$2:$O$51,0)</f>
+        <v/>
+      </c>
+      <c r="T11">
+        <f>INDEX($N$2:$N$51,$S11)</f>
+        <v/>
+      </c>
+      <c r="U11">
+        <f>INDEX($M$2:$M$51,$S11)</f>
+        <v/>
+      </c>
+      <c r="V11">
+        <f>MATCH(LARGE($R$2:$R$51,10),$R$2:$R$51,0)</f>
+        <v/>
+      </c>
+      <c r="W11">
+        <f>INDEX($Q$2:$Q$51,$V11)</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>INDEX($P$2:$P$51,$V11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="M12">
+        <f>IFERROR(INDEX(Kategorier,11),"")</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>IF($M12="",0,COUNTIFS(Saker!$F$2:$F$501,$M12))</f>
+        <v/>
+      </c>
+      <c r="O12">
+        <f>IF($N12=0,-999999,$N12-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P12">
+        <f>IFERROR(INDEX(Ansatte,11),"")</f>
+        <v/>
+      </c>
+      <c r="Q12">
+        <f>IF($P12="",0,COUNTIFS(Saker!$L$2:$L$501,$P12))</f>
+        <v/>
+      </c>
+      <c r="R12">
+        <f>IF($Q12=0,-999999,$Q12-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="M13">
+        <f>IFERROR(INDEX(Kategorier,12),"")</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>IF($M13="",0,COUNTIFS(Saker!$F$2:$F$501,$M13))</f>
+        <v/>
+      </c>
+      <c r="O13">
+        <f>IF($N13=0,-999999,$N13-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P13">
+        <f>IFERROR(INDEX(Ansatte,12),"")</f>
+        <v/>
+      </c>
+      <c r="Q13">
+        <f>IF($P13="",0,COUNTIFS(Saker!$L$2:$L$501,$P13))</f>
+        <v/>
+      </c>
+      <c r="R13">
+        <f>IF($Q13=0,-999999,$Q13-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="M14">
+        <f>IFERROR(INDEX(Kategorier,13),"")</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>IF($M14="",0,COUNTIFS(Saker!$F$2:$F$501,$M14))</f>
+        <v/>
+      </c>
+      <c r="O14">
+        <f>IF($N14=0,-999999,$N14-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P14">
+        <f>IFERROR(INDEX(Ansatte,13),"")</f>
+        <v/>
+      </c>
+      <c r="Q14">
+        <f>IF($P14="",0,COUNTIFS(Saker!$L$2:$L$501,$P14))</f>
+        <v/>
+      </c>
+      <c r="R14">
+        <f>IF($Q14=0,-999999,$Q14-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="M15">
+        <f>IFERROR(INDEX(Kategorier,14),"")</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>IF($M15="",0,COUNTIFS(Saker!$F$2:$F$501,$M15))</f>
+        <v/>
+      </c>
+      <c r="O15">
+        <f>IF($N15=0,-999999,$N15-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P15">
+        <f>IFERROR(INDEX(Ansatte,14),"")</f>
+        <v/>
+      </c>
+      <c r="Q15">
+        <f>IF($P15="",0,COUNTIFS(Saker!$L$2:$L$501,$P15))</f>
+        <v/>
+      </c>
+      <c r="R15">
+        <f>IF($Q15=0,-999999,$Q15-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="M16">
+        <f>IFERROR(INDEX(Kategorier,15),"")</f>
+        <v/>
+      </c>
+      <c r="N16">
+        <f>IF($M16="",0,COUNTIFS(Saker!$F$2:$F$501,$M16))</f>
+        <v/>
+      </c>
+      <c r="O16">
+        <f>IF($N16=0,-999999,$N16-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P16">
+        <f>IFERROR(INDEX(Ansatte,15),"")</f>
+        <v/>
+      </c>
+      <c r="Q16">
+        <f>IF($P16="",0,COUNTIFS(Saker!$L$2:$L$501,$P16))</f>
+        <v/>
+      </c>
+      <c r="R16">
+        <f>IF($Q16=0,-999999,$Q16-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="M17">
+        <f>IFERROR(INDEX(Kategorier,16),"")</f>
+        <v/>
+      </c>
+      <c r="N17">
+        <f>IF($M17="",0,COUNTIFS(Saker!$F$2:$F$501,$M17))</f>
+        <v/>
+      </c>
+      <c r="O17">
+        <f>IF($N17=0,-999999,$N17-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P17">
+        <f>IFERROR(INDEX(Ansatte,16),"")</f>
+        <v/>
+      </c>
+      <c r="Q17">
+        <f>IF($P17="",0,COUNTIFS(Saker!$L$2:$L$501,$P17))</f>
+        <v/>
+      </c>
+      <c r="R17">
+        <f>IF($Q17=0,-999999,$Q17-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="M18">
+        <f>IFERROR(INDEX(Kategorier,17),"")</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>IF($M18="",0,COUNTIFS(Saker!$F$2:$F$501,$M18))</f>
+        <v/>
+      </c>
+      <c r="O18">
+        <f>IF($N18=0,-999999,$N18-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P18">
+        <f>IFERROR(INDEX(Ansatte,17),"")</f>
+        <v/>
+      </c>
+      <c r="Q18">
+        <f>IF($P18="",0,COUNTIFS(Saker!$L$2:$L$501,$P18))</f>
+        <v/>
+      </c>
+      <c r="R18">
+        <f>IF($Q18=0,-999999,$Q18-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="M19">
+        <f>IFERROR(INDEX(Kategorier,18),"")</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>IF($M19="",0,COUNTIFS(Saker!$F$2:$F$501,$M19))</f>
+        <v/>
+      </c>
+      <c r="O19">
+        <f>IF($N19=0,-999999,$N19-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P19">
+        <f>IFERROR(INDEX(Ansatte,18),"")</f>
+        <v/>
+      </c>
+      <c r="Q19">
+        <f>IF($P19="",0,COUNTIFS(Saker!$L$2:$L$501,$P19))</f>
+        <v/>
+      </c>
+      <c r="R19">
+        <f>IF($Q19=0,-999999,$Q19-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="M20">
+        <f>IFERROR(INDEX(Kategorier,19),"")</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>IF($M20="",0,COUNTIFS(Saker!$F$2:$F$501,$M20))</f>
+        <v/>
+      </c>
+      <c r="O20">
+        <f>IF($N20=0,-999999,$N20-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P20">
+        <f>IFERROR(INDEX(Ansatte,19),"")</f>
+        <v/>
+      </c>
+      <c r="Q20">
+        <f>IF($P20="",0,COUNTIFS(Saker!$L$2:$L$501,$P20))</f>
+        <v/>
+      </c>
+      <c r="R20">
+        <f>IF($Q20=0,-999999,$Q20-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="M21">
+        <f>IFERROR(INDEX(Kategorier,20),"")</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>IF($M21="",0,COUNTIFS(Saker!$F$2:$F$501,$M21))</f>
+        <v/>
+      </c>
+      <c r="O21">
+        <f>IF($N21=0,-999999,$N21-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P21">
+        <f>IFERROR(INDEX(Ansatte,20),"")</f>
+        <v/>
+      </c>
+      <c r="Q21">
+        <f>IF($P21="",0,COUNTIFS(Saker!$L$2:$L$501,$P21))</f>
+        <v/>
+      </c>
+      <c r="R21">
+        <f>IF($Q21=0,-999999,$Q21-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="M22">
+        <f>IFERROR(INDEX(Kategorier,21),"")</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>IF($M22="",0,COUNTIFS(Saker!$F$2:$F$501,$M22))</f>
+        <v/>
+      </c>
+      <c r="O22">
+        <f>IF($N22=0,-999999,$N22-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P22">
+        <f>IFERROR(INDEX(Ansatte,21),"")</f>
+        <v/>
+      </c>
+      <c r="Q22">
+        <f>IF($P22="",0,COUNTIFS(Saker!$L$2:$L$501,$P22))</f>
+        <v/>
+      </c>
+      <c r="R22">
+        <f>IF($Q22=0,-999999,$Q22-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="M23">
+        <f>IFERROR(INDEX(Kategorier,22),"")</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>IF($M23="",0,COUNTIFS(Saker!$F$2:$F$501,$M23))</f>
+        <v/>
+      </c>
+      <c r="O23">
+        <f>IF($N23=0,-999999,$N23-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P23">
+        <f>IFERROR(INDEX(Ansatte,22),"")</f>
+        <v/>
+      </c>
+      <c r="Q23">
+        <f>IF($P23="",0,COUNTIFS(Saker!$L$2:$L$501,$P23))</f>
+        <v/>
+      </c>
+      <c r="R23">
+        <f>IF($Q23=0,-999999,$Q23-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="M24">
+        <f>IFERROR(INDEX(Kategorier,23),"")</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>IF($M24="",0,COUNTIFS(Saker!$F$2:$F$501,$M24))</f>
+        <v/>
+      </c>
+      <c r="O24">
+        <f>IF($N24=0,-999999,$N24-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P24">
+        <f>IFERROR(INDEX(Ansatte,23),"")</f>
+        <v/>
+      </c>
+      <c r="Q24">
+        <f>IF($P24="",0,COUNTIFS(Saker!$L$2:$L$501,$P24))</f>
+        <v/>
+      </c>
+      <c r="R24">
+        <f>IF($Q24=0,-999999,$Q24-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="M25">
+        <f>IFERROR(INDEX(Kategorier,24),"")</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>IF($M25="",0,COUNTIFS(Saker!$F$2:$F$501,$M25))</f>
+        <v/>
+      </c>
+      <c r="O25">
+        <f>IF($N25=0,-999999,$N25-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P25">
+        <f>IFERROR(INDEX(Ansatte,24),"")</f>
+        <v/>
+      </c>
+      <c r="Q25">
+        <f>IF($P25="",0,COUNTIFS(Saker!$L$2:$L$501,$P25))</f>
+        <v/>
+      </c>
+      <c r="R25">
+        <f>IF($Q25=0,-999999,$Q25-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Saker per status</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Saker per ansvarlig</t>
-        </is>
+      <c r="C26" s="6">
+        <f>"Topp "&amp;MIN(10,COUNTIFS($Q$2:$Q$51,"&gt;0"))&amp;" saker pr ansvarlig"</f>
+        <v/>
+      </c>
+      <c r="M26">
+        <f>IFERROR(INDEX(Kategorier,25),"")</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>IF($M26="",0,COUNTIFS(Saker!$F$2:$F$501,$M26))</f>
+        <v/>
+      </c>
+      <c r="O26">
+        <f>IF($N26=0,-999999,$N26-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P26">
+        <f>IFERROR(INDEX(Ansatte,25),"")</f>
+        <v/>
+      </c>
+      <c r="Q26">
+        <f>IF($P26="",0,COUNTIFS(Saker!$L$2:$L$501,$P26))</f>
+        <v/>
+      </c>
+      <c r="R26">
+        <f>IF($Q26=0,-999999,$Q26-ROW()/1000000)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1585,13 +2474,36 @@
         <f>COUNTIFS(Saker!$M$2:$M$501,$A27)</f>
         <v/>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Ola Nordmann</t>
-        </is>
+      <c r="C27" s="7">
+        <f>IF($W2&gt;0,$X2,"")</f>
+        <v/>
       </c>
       <c r="D27" s="7">
-        <f>COUNTIFS(Saker!$L$2:$L$501,$C27)</f>
+        <f>IF($W2&gt;0,$W2,"")</f>
+        <v/>
+      </c>
+      <c r="M27">
+        <f>IFERROR(INDEX(Kategorier,26),"")</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>IF($M27="",0,COUNTIFS(Saker!$F$2:$F$501,$M27))</f>
+        <v/>
+      </c>
+      <c r="O27">
+        <f>IF($N27=0,-999999,$N27-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P27">
+        <f>IFERROR(INDEX(Ansatte,26),"")</f>
+        <v/>
+      </c>
+      <c r="Q27">
+        <f>IF($P27="",0,COUNTIFS(Saker!$L$2:$L$501,$P27))</f>
+        <v/>
+      </c>
+      <c r="R27">
+        <f>IF($Q27=0,-999999,$Q27-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -1605,13 +2517,36 @@
         <f>COUNTIFS(Saker!$M$2:$M$501,$A28)</f>
         <v/>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Kari Hansen</t>
-        </is>
+      <c r="C28" s="7">
+        <f>IF($W3&gt;0,$X3,"")</f>
+        <v/>
       </c>
       <c r="D28" s="7">
-        <f>COUNTIFS(Saker!$L$2:$L$501,$C28)</f>
+        <f>IF($W3&gt;0,$W3,"")</f>
+        <v/>
+      </c>
+      <c r="M28">
+        <f>IFERROR(INDEX(Kategorier,27),"")</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>IF($M28="",0,COUNTIFS(Saker!$F$2:$F$501,$M28))</f>
+        <v/>
+      </c>
+      <c r="O28">
+        <f>IF($N28=0,-999999,$N28-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P28">
+        <f>IFERROR(INDEX(Ansatte,27),"")</f>
+        <v/>
+      </c>
+      <c r="Q28">
+        <f>IF($P28="",0,COUNTIFS(Saker!$L$2:$L$501,$P28))</f>
+        <v/>
+      </c>
+      <c r="R28">
+        <f>IF($Q28=0,-999999,$Q28-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -1625,13 +2560,36 @@
         <f>COUNTIFS(Saker!$M$2:$M$501,$A29)</f>
         <v/>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Per Olsen</t>
-        </is>
+      <c r="C29" s="7">
+        <f>IF($W4&gt;0,$X4,"")</f>
+        <v/>
       </c>
       <c r="D29" s="7">
-        <f>COUNTIFS(Saker!$L$2:$L$501,$C29)</f>
+        <f>IF($W4&gt;0,$W4,"")</f>
+        <v/>
+      </c>
+      <c r="M29">
+        <f>IFERROR(INDEX(Kategorier,28),"")</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>IF($M29="",0,COUNTIFS(Saker!$F$2:$F$501,$M29))</f>
+        <v/>
+      </c>
+      <c r="O29">
+        <f>IF($N29=0,-999999,$N29-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P29">
+        <f>IFERROR(INDEX(Ansatte,28),"")</f>
+        <v/>
+      </c>
+      <c r="Q29">
+        <f>IF($P29="",0,COUNTIFS(Saker!$L$2:$L$501,$P29))</f>
+        <v/>
+      </c>
+      <c r="R29">
+        <f>IF($Q29=0,-999999,$Q29-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -1645,13 +2603,36 @@
         <f>COUNTIFS(Saker!$M$2:$M$501,$A30)</f>
         <v/>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Anne Berg</t>
-        </is>
+      <c r="C30" s="7">
+        <f>IF($W5&gt;0,$X5,"")</f>
+        <v/>
       </c>
       <c r="D30" s="7">
-        <f>COUNTIFS(Saker!$L$2:$L$501,$C30)</f>
+        <f>IF($W5&gt;0,$W5,"")</f>
+        <v/>
+      </c>
+      <c r="M30">
+        <f>IFERROR(INDEX(Kategorier,29),"")</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>IF($M30="",0,COUNTIFS(Saker!$F$2:$F$501,$M30))</f>
+        <v/>
+      </c>
+      <c r="O30">
+        <f>IF($N30=0,-999999,$N30-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P30">
+        <f>IFERROR(INDEX(Ansatte,29),"")</f>
+        <v/>
+      </c>
+      <c r="Q30">
+        <f>IF($P30="",0,COUNTIFS(Saker!$L$2:$L$501,$P30))</f>
+        <v/>
+      </c>
+      <c r="R30">
+        <f>IF($Q30=0,-999999,$Q30-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -1665,13 +2646,36 @@
         <f>COUNTIFS(Saker!$M$2:$M$501,$A31)</f>
         <v/>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Erik Dahl</t>
-        </is>
+      <c r="C31" s="7">
+        <f>IF($W6&gt;0,$X6,"")</f>
+        <v/>
       </c>
       <c r="D31" s="7">
-        <f>COUNTIFS(Saker!$L$2:$L$501,$C31)</f>
+        <f>IF($W6&gt;0,$W6,"")</f>
+        <v/>
+      </c>
+      <c r="M31">
+        <f>IFERROR(INDEX(Kategorier,30),"")</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>IF($M31="",0,COUNTIFS(Saker!$F$2:$F$501,$M31))</f>
+        <v/>
+      </c>
+      <c r="O31">
+        <f>IF($N31=0,-999999,$N31-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P31">
+        <f>IFERROR(INDEX(Ansatte,30),"")</f>
+        <v/>
+      </c>
+      <c r="Q31">
+        <f>IF($P31="",0,COUNTIFS(Saker!$L$2:$L$501,$P31))</f>
+        <v/>
+      </c>
+      <c r="R31">
+        <f>IF($Q31=0,-999999,$Q31-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -1685,109 +2689,646 @@
         <f>COUNTIFS(Saker!$M$2:$M$501,$A32)</f>
         <v/>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Mona Lie</t>
-        </is>
+      <c r="C32" s="7">
+        <f>IF($W7&gt;0,$X7,"")</f>
+        <v/>
       </c>
       <c r="D32" s="7">
-        <f>COUNTIFS(Saker!$L$2:$L$501,$C32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="12" customHeight="1"/>
+        <f>IF($W7&gt;0,$W7,"")</f>
+        <v/>
+      </c>
+      <c r="M32">
+        <f>IFERROR(INDEX(Kategorier,31),"")</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>IF($M32="",0,COUNTIFS(Saker!$F$2:$F$501,$M32))</f>
+        <v/>
+      </c>
+      <c r="O32">
+        <f>IF($N32=0,-999999,$N32-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P32">
+        <f>IFERROR(INDEX(Ansatte,31),"")</f>
+        <v/>
+      </c>
+      <c r="Q32">
+        <f>IF($P32="",0,COUNTIFS(Saker!$L$2:$L$501,$P32))</f>
+        <v/>
+      </c>
+      <c r="R32">
+        <f>IF($Q32=0,-999999,$Q32-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="12" customHeight="1">
+      <c r="C33" s="7">
+        <f>IF($W8&gt;0,$X8,"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="7">
+        <f>IF($W8&gt;0,$W8,"")</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>IFERROR(INDEX(Kategorier,32),"")</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>IF($M33="",0,COUNTIFS(Saker!$F$2:$F$501,$M33))</f>
+        <v/>
+      </c>
+      <c r="O33">
+        <f>IF($N33=0,-999999,$N33-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P33">
+        <f>IFERROR(INDEX(Ansatte,32),"")</f>
+        <v/>
+      </c>
+      <c r="Q33">
+        <f>IF($P33="",0,COUNTIFS(Saker!$L$2:$L$501,$P33))</f>
+        <v/>
+      </c>
+      <c r="R33">
+        <f>IF($Q33=0,-999999,$Q33-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Saker per kategori</t>
-        </is>
+      <c r="A34" s="6">
+        <f>"Topp "&amp;MIN(10,COUNTIFS($N$2:$N$51,"&gt;0"))&amp;" saker pr kategori"</f>
+        <v/>
+      </c>
+      <c r="C34" s="7">
+        <f>IF($W9&gt;0,$X9,"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="7">
+        <f>IF($W9&gt;0,$W9,"")</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>IFERROR(INDEX(Kategorier,33),"")</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>IF($M34="",0,COUNTIFS(Saker!$F$2:$F$501,$M34))</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>IF($N34=0,-999999,$N34-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>IFERROR(INDEX(Ansatte,33),"")</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>IF($P34="",0,COUNTIFS(Saker!$L$2:$L$501,$P34))</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>IF($Q34=0,-999999,$Q34-ROW()/1000000)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Nettverk</t>
-        </is>
+      <c r="A35" s="7">
+        <f>IF($T2&gt;0,$U2,"")</f>
+        <v/>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A35)</f>
+        <f>IF($T2&gt;0,$T2,"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="7">
+        <f>IF($W10&gt;0,$X10,"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="7">
+        <f>IF($W10&gt;0,$W10,"")</f>
+        <v/>
+      </c>
+      <c r="M35">
+        <f>IFERROR(INDEX(Kategorier,34),"")</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>IF($M35="",0,COUNTIFS(Saker!$F$2:$F$501,$M35))</f>
+        <v/>
+      </c>
+      <c r="O35">
+        <f>IF($N35=0,-999999,$N35-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P35">
+        <f>IFERROR(INDEX(Ansatte,34),"")</f>
+        <v/>
+      </c>
+      <c r="Q35">
+        <f>IF($P35="",0,COUNTIFS(Saker!$L$2:$L$501,$P35))</f>
+        <v/>
+      </c>
+      <c r="R35">
+        <f>IF($Q35=0,-999999,$Q35-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Passord og tilgang</t>
-        </is>
+      <c r="A36" s="7">
+        <f>IF($T3&gt;0,$U3,"")</f>
+        <v/>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A36)</f>
+        <f>IF($T3&gt;0,$T3,"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="7">
+        <f>IF($W11&gt;0,$X11,"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="7">
+        <f>IF($W11&gt;0,$W11,"")</f>
+        <v/>
+      </c>
+      <c r="M36">
+        <f>IFERROR(INDEX(Kategorier,35),"")</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>IF($M36="",0,COUNTIFS(Saker!$F$2:$F$501,$M36))</f>
+        <v/>
+      </c>
+      <c r="O36">
+        <f>IF($N36=0,-999999,$N36-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P36">
+        <f>IFERROR(INDEX(Ansatte,35),"")</f>
+        <v/>
+      </c>
+      <c r="Q36">
+        <f>IF($P36="",0,COUNTIFS(Saker!$L$2:$L$501,$P36))</f>
+        <v/>
+      </c>
+      <c r="R36">
+        <f>IF($Q36=0,-999999,$Q36-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>E-post og kalender</t>
-        </is>
+      <c r="A37" s="7">
+        <f>IF($T4&gt;0,$U4,"")</f>
+        <v/>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A37)</f>
+        <f>IF($T4&gt;0,$T4,"")</f>
+        <v/>
+      </c>
+      <c r="M37">
+        <f>IFERROR(INDEX(Kategorier,36),"")</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>IF($M37="",0,COUNTIFS(Saker!$F$2:$F$501,$M37))</f>
+        <v/>
+      </c>
+      <c r="O37">
+        <f>IF($N37=0,-999999,$N37-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P37">
+        <f>IFERROR(INDEX(Ansatte,36),"")</f>
+        <v/>
+      </c>
+      <c r="Q37">
+        <f>IF($P37="",0,COUNTIFS(Saker!$L$2:$L$501,$P37))</f>
+        <v/>
+      </c>
+      <c r="R37">
+        <f>IF($Q37=0,-999999,$Q37-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Maskinvare</t>
-        </is>
+      <c r="A38" s="7">
+        <f>IF($T5&gt;0,$U5,"")</f>
+        <v/>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A38)</f>
+        <f>IF($T5&gt;0,$T5,"")</f>
+        <v/>
+      </c>
+      <c r="M38">
+        <f>IFERROR(INDEX(Kategorier,37),"")</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>IF($M38="",0,COUNTIFS(Saker!$F$2:$F$501,$M38))</f>
+        <v/>
+      </c>
+      <c r="O38">
+        <f>IF($N38=0,-999999,$N38-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P38">
+        <f>IFERROR(INDEX(Ansatte,37),"")</f>
+        <v/>
+      </c>
+      <c r="Q38">
+        <f>IF($P38="",0,COUNTIFS(Saker!$L$2:$L$501,$P38))</f>
+        <v/>
+      </c>
+      <c r="R38">
+        <f>IF($Q38=0,-999999,$Q38-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Programvare</t>
-        </is>
+      <c r="A39" s="7">
+        <f>IF($T6&gt;0,$U6,"")</f>
+        <v/>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A39)</f>
+        <f>IF($T6&gt;0,$T6,"")</f>
+        <v/>
+      </c>
+      <c r="M39">
+        <f>IFERROR(INDEX(Kategorier,38),"")</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>IF($M39="",0,COUNTIFS(Saker!$F$2:$F$501,$M39))</f>
+        <v/>
+      </c>
+      <c r="O39">
+        <f>IF($N39=0,-999999,$N39-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P39">
+        <f>IFERROR(INDEX(Ansatte,38),"")</f>
+        <v/>
+      </c>
+      <c r="Q39">
+        <f>IF($P39="",0,COUNTIFS(Saker!$L$2:$L$501,$P39))</f>
+        <v/>
+      </c>
+      <c r="R39">
+        <f>IF($Q39=0,-999999,$Q39-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Skriver og utskrift</t>
-        </is>
+      <c r="A40" s="7">
+        <f>IF($T7&gt;0,$U7,"")</f>
+        <v/>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A40)</f>
+        <f>IF($T7&gt;0,$T7,"")</f>
+        <v/>
+      </c>
+      <c r="M40">
+        <f>IFERROR(INDEX(Kategorier,39),"")</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>IF($M40="",0,COUNTIFS(Saker!$F$2:$F$501,$M40))</f>
+        <v/>
+      </c>
+      <c r="O40">
+        <f>IF($N40=0,-999999,$N40-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P40">
+        <f>IFERROR(INDEX(Ansatte,39),"")</f>
+        <v/>
+      </c>
+      <c r="Q40">
+        <f>IF($P40="",0,COUNTIFS(Saker!$L$2:$L$501,$P40))</f>
+        <v/>
+      </c>
+      <c r="R40">
+        <f>IF($Q40=0,-999999,$Q40-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Mobil og telefoni</t>
-        </is>
+      <c r="A41" s="7">
+        <f>IF($T8&gt;0,$U8,"")</f>
+        <v/>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A41)</f>
+        <f>IF($T8&gt;0,$T8,"")</f>
+        <v/>
+      </c>
+      <c r="M41">
+        <f>IFERROR(INDEX(Kategorier,40),"")</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>IF($M41="",0,COUNTIFS(Saker!$F$2:$F$501,$M41))</f>
+        <v/>
+      </c>
+      <c r="O41">
+        <f>IF($N41=0,-999999,$N41-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P41">
+        <f>IFERROR(INDEX(Ansatte,40),"")</f>
+        <v/>
+      </c>
+      <c r="Q41">
+        <f>IF($P41="",0,COUNTIFS(Saker!$L$2:$L$501,$P41))</f>
+        <v/>
+      </c>
+      <c r="R41">
+        <f>IF($Q41=0,-999999,$Q41-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Annet</t>
-        </is>
+      <c r="A42" s="7">
+        <f>IF($T9&gt;0,$U9,"")</f>
+        <v/>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIFS(Saker!$F$2:$F$501,$A42)</f>
+        <f>IF($T9&gt;0,$T9,"")</f>
+        <v/>
+      </c>
+      <c r="M42">
+        <f>IFERROR(INDEX(Kategorier,41),"")</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>IF($M42="",0,COUNTIFS(Saker!$F$2:$F$501,$M42))</f>
+        <v/>
+      </c>
+      <c r="O42">
+        <f>IF($N42=0,-999999,$N42-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P42">
+        <f>IFERROR(INDEX(Ansatte,41),"")</f>
+        <v/>
+      </c>
+      <c r="Q42">
+        <f>IF($P42="",0,COUNTIFS(Saker!$L$2:$L$501,$P42))</f>
+        <v/>
+      </c>
+      <c r="R42">
+        <f>IF($Q42=0,-999999,$Q42-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7">
+        <f>IF($T10&gt;0,$U10,"")</f>
+        <v/>
+      </c>
+      <c r="B43" s="7">
+        <f>IF($T10&gt;0,$T10,"")</f>
+        <v/>
+      </c>
+      <c r="M43">
+        <f>IFERROR(INDEX(Kategorier,42),"")</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>IF($M43="",0,COUNTIFS(Saker!$F$2:$F$501,$M43))</f>
+        <v/>
+      </c>
+      <c r="O43">
+        <f>IF($N43=0,-999999,$N43-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P43">
+        <f>IFERROR(INDEX(Ansatte,42),"")</f>
+        <v/>
+      </c>
+      <c r="Q43">
+        <f>IF($P43="",0,COUNTIFS(Saker!$L$2:$L$501,$P43))</f>
+        <v/>
+      </c>
+      <c r="R43">
+        <f>IF($Q43=0,-999999,$Q43-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7">
+        <f>IF($T11&gt;0,$U11,"")</f>
+        <v/>
+      </c>
+      <c r="B44" s="7">
+        <f>IF($T11&gt;0,$T11,"")</f>
+        <v/>
+      </c>
+      <c r="M44">
+        <f>IFERROR(INDEX(Kategorier,43),"")</f>
+        <v/>
+      </c>
+      <c r="N44">
+        <f>IF($M44="",0,COUNTIFS(Saker!$F$2:$F$501,$M44))</f>
+        <v/>
+      </c>
+      <c r="O44">
+        <f>IF($N44=0,-999999,$N44-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P44">
+        <f>IFERROR(INDEX(Ansatte,43),"")</f>
+        <v/>
+      </c>
+      <c r="Q44">
+        <f>IF($P44="",0,COUNTIFS(Saker!$L$2:$L$501,$P44))</f>
+        <v/>
+      </c>
+      <c r="R44">
+        <f>IF($Q44=0,-999999,$Q44-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="M45">
+        <f>IFERROR(INDEX(Kategorier,44),"")</f>
+        <v/>
+      </c>
+      <c r="N45">
+        <f>IF($M45="",0,COUNTIFS(Saker!$F$2:$F$501,$M45))</f>
+        <v/>
+      </c>
+      <c r="O45">
+        <f>IF($N45=0,-999999,$N45-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P45">
+        <f>IFERROR(INDEX(Ansatte,44),"")</f>
+        <v/>
+      </c>
+      <c r="Q45">
+        <f>IF($P45="",0,COUNTIFS(Saker!$L$2:$L$501,$P45))</f>
+        <v/>
+      </c>
+      <c r="R45">
+        <f>IF($Q45=0,-999999,$Q45-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="M46">
+        <f>IFERROR(INDEX(Kategorier,45),"")</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>IF($M46="",0,COUNTIFS(Saker!$F$2:$F$501,$M46))</f>
+        <v/>
+      </c>
+      <c r="O46">
+        <f>IF($N46=0,-999999,$N46-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P46">
+        <f>IFERROR(INDEX(Ansatte,45),"")</f>
+        <v/>
+      </c>
+      <c r="Q46">
+        <f>IF($P46="",0,COUNTIFS(Saker!$L$2:$L$501,$P46))</f>
+        <v/>
+      </c>
+      <c r="R46">
+        <f>IF($Q46=0,-999999,$Q46-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="M47">
+        <f>IFERROR(INDEX(Kategorier,46),"")</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>IF($M47="",0,COUNTIFS(Saker!$F$2:$F$501,$M47))</f>
+        <v/>
+      </c>
+      <c r="O47">
+        <f>IF($N47=0,-999999,$N47-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P47">
+        <f>IFERROR(INDEX(Ansatte,46),"")</f>
+        <v/>
+      </c>
+      <c r="Q47">
+        <f>IF($P47="",0,COUNTIFS(Saker!$L$2:$L$501,$P47))</f>
+        <v/>
+      </c>
+      <c r="R47">
+        <f>IF($Q47=0,-999999,$Q47-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="M48">
+        <f>IFERROR(INDEX(Kategorier,47),"")</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>IF($M48="",0,COUNTIFS(Saker!$F$2:$F$501,$M48))</f>
+        <v/>
+      </c>
+      <c r="O48">
+        <f>IF($N48=0,-999999,$N48-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P48">
+        <f>IFERROR(INDEX(Ansatte,47),"")</f>
+        <v/>
+      </c>
+      <c r="Q48">
+        <f>IF($P48="",0,COUNTIFS(Saker!$L$2:$L$501,$P48))</f>
+        <v/>
+      </c>
+      <c r="R48">
+        <f>IF($Q48=0,-999999,$Q48-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="M49">
+        <f>IFERROR(INDEX(Kategorier,48),"")</f>
+        <v/>
+      </c>
+      <c r="N49">
+        <f>IF($M49="",0,COUNTIFS(Saker!$F$2:$F$501,$M49))</f>
+        <v/>
+      </c>
+      <c r="O49">
+        <f>IF($N49=0,-999999,$N49-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P49">
+        <f>IFERROR(INDEX(Ansatte,48),"")</f>
+        <v/>
+      </c>
+      <c r="Q49">
+        <f>IF($P49="",0,COUNTIFS(Saker!$L$2:$L$501,$P49))</f>
+        <v/>
+      </c>
+      <c r="R49">
+        <f>IF($Q49=0,-999999,$Q49-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="M50">
+        <f>IFERROR(INDEX(Kategorier,49),"")</f>
+        <v/>
+      </c>
+      <c r="N50">
+        <f>IF($M50="",0,COUNTIFS(Saker!$F$2:$F$501,$M50))</f>
+        <v/>
+      </c>
+      <c r="O50">
+        <f>IF($N50=0,-999999,$N50-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P50">
+        <f>IFERROR(INDEX(Ansatte,49),"")</f>
+        <v/>
+      </c>
+      <c r="Q50">
+        <f>IF($P50="",0,COUNTIFS(Saker!$L$2:$L$501,$P50))</f>
+        <v/>
+      </c>
+      <c r="R50">
+        <f>IF($Q50=0,-999999,$Q50-ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="M51">
+        <f>IFERROR(INDEX(Kategorier,50),"")</f>
+        <v/>
+      </c>
+      <c r="N51">
+        <f>IF($M51="",0,COUNTIFS(Saker!$F$2:$F$501,$M51))</f>
+        <v/>
+      </c>
+      <c r="O51">
+        <f>IF($N51=0,-999999,$N51-ROW()/1000000)</f>
+        <v/>
+      </c>
+      <c r="P51">
+        <f>IFERROR(INDEX(Ansatte,50),"")</f>
+        <v/>
+      </c>
+      <c r="Q51">
+        <f>IF($P51="",0,COUNTIFS(Saker!$L$2:$L$501,$P51))</f>
+        <v/>
+      </c>
+      <c r="R51">
+        <f>IF($Q51=0,-999999,$Q51-ROW()/1000000)</f>
         <v/>
       </c>
     </row>
